--- a/Team-Data/2012-13/2-22-2012-13.xlsx
+++ b/Team-Data/2012-13/2-22-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,37 +728,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F2" t="n">
         <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
       </c>
       <c r="I2" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J2" t="n">
-        <v>80.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.463</v>
+        <v>0.461</v>
       </c>
       <c r="L2" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="M2" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.38</v>
+        <v>0.379</v>
       </c>
       <c r="O2" t="n">
         <v>13.6</v>
@@ -700,64 +767,64 @@
         <v>19.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7</v>
+        <v>0.701</v>
       </c>
       <c r="R2" t="n">
         <v>9.5</v>
       </c>
       <c r="S2" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="T2" t="n">
         <v>40.9</v>
       </c>
       <c r="U2" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="V2" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="W2" t="n">
         <v>7.9</v>
       </c>
       <c r="X2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AA2" t="n">
         <v>19</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.3</v>
+        <v>96.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
         <v>14</v>
       </c>
       <c r="AF2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK2" t="n">
         <v>7</v>
@@ -775,7 +842,7 @@
         <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AQ2" t="n">
         <v>27</v>
@@ -784,10 +851,10 @@
         <v>27</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
@@ -799,10 +866,10 @@
         <v>15</v>
       </c>
       <c r="AX2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
         <v>2</v>
@@ -811,10 +878,10 @@
         <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -843,70 +910,70 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" t="n">
         <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>0.527</v>
+        <v>0.519</v>
       </c>
       <c r="H3" t="n">
         <v>49.3</v>
       </c>
       <c r="I3" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J3" t="n">
         <v>80.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M3" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.345</v>
+        <v>0.343</v>
       </c>
       <c r="O3" t="n">
         <v>16.4</v>
       </c>
       <c r="P3" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.779</v>
+        <v>0.782</v>
       </c>
       <c r="R3" t="n">
         <v>8.5</v>
       </c>
       <c r="S3" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="T3" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="U3" t="n">
         <v>23.3</v>
       </c>
       <c r="V3" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W3" t="n">
         <v>8.6</v>
       </c>
       <c r="X3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z3" t="n">
         <v>21.6</v>
@@ -915,13 +982,13 @@
         <v>19.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>96.09999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
         <v>15</v>
@@ -942,37 +1009,37 @@
         <v>26</v>
       </c>
       <c r="AK3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL3" t="n">
         <v>26</v>
       </c>
       <c r="AM3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN3" t="n">
         <v>26</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AO3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP3" t="n">
         <v>23</v>
       </c>
-      <c r="AO3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>22</v>
-      </c>
       <c r="AQ3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AR3" t="n">
         <v>29</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
         <v>9</v>
@@ -996,7 +1063,7 @@
         <v>18</v>
       </c>
       <c r="BC3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -1025,58 +1092,58 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E4" t="n">
         <v>33</v>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>0.589</v>
+        <v>0.6</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="J4" t="n">
-        <v>79.5</v>
+        <v>79.3</v>
       </c>
       <c r="K4" t="n">
         <v>0.441</v>
       </c>
       <c r="L4" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M4" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O4" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="P4" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.739</v>
+        <v>0.741</v>
       </c>
       <c r="R4" t="n">
         <v>12.5</v>
       </c>
       <c r="S4" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T4" t="n">
         <v>42.3</v>
       </c>
       <c r="U4" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V4" t="n">
         <v>14.6</v>
@@ -1091,22 +1158,22 @@
         <v>4.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AA4" t="n">
         <v>21.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="AD4" t="n">
         <v>5</v>
       </c>
       <c r="AE4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF4" t="n">
         <v>9</v>
@@ -1133,13 +1200,13 @@
         <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ4" t="n">
         <v>21</v>
@@ -1148,7 +1215,7 @@
         <v>9</v>
       </c>
       <c r="AS4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT4" t="n">
         <v>15</v>
@@ -1157,13 +1224,13 @@
         <v>27</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY4" t="n">
         <v>8</v>
@@ -1178,7 +1245,7 @@
         <v>19</v>
       </c>
       <c r="BC4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -1207,46 +1274,46 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" t="n">
         <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>0.236</v>
+        <v>0.241</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
       </c>
       <c r="I5" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="J5" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.42</v>
+        <v>0.421</v>
       </c>
       <c r="L5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="M5" t="n">
         <v>16.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.349</v>
+        <v>0.351</v>
       </c>
       <c r="O5" t="n">
         <v>19.4</v>
       </c>
       <c r="P5" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.748</v>
+        <v>0.751</v>
       </c>
       <c r="R5" t="n">
         <v>11.5</v>
@@ -1258,10 +1325,10 @@
         <v>41.2</v>
       </c>
       <c r="U5" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="V5" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W5" t="n">
         <v>7.1</v>
@@ -1273,19 +1340,19 @@
         <v>7.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1297,13 +1364,13 @@
         <v>30</v>
       </c>
       <c r="AH5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI5" t="n">
         <v>30</v>
       </c>
       <c r="AJ5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1312,10 +1379,10 @@
         <v>25</v>
       </c>
       <c r="AM5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AO5" t="n">
         <v>2</v>
@@ -1342,7 +1409,7 @@
         <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1357,7 +1424,7 @@
         <v>4</v>
       </c>
       <c r="BB5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" t="n">
         <v>23</v>
       </c>
       <c r="G6" t="n">
-        <v>0.582</v>
+        <v>0.574</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J6" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L6" t="n">
         <v>4.7</v>
@@ -1428,7 +1495,7 @@
         <v>21.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.78</v>
+        <v>0.779</v>
       </c>
       <c r="R6" t="n">
         <v>12.8</v>
@@ -1440,10 +1507,10 @@
         <v>43.7</v>
       </c>
       <c r="U6" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="V6" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W6" t="n">
         <v>7.3</v>
@@ -1455,31 +1522,31 @@
         <v>5.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA6" t="n">
         <v>20.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG6" t="n">
         <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI6" t="n">
         <v>25</v>
@@ -1488,10 +1555,10 @@
         <v>22</v>
       </c>
       <c r="AK6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM6" t="n">
         <v>29</v>
@@ -1506,28 +1573,28 @@
         <v>17</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT6" t="n">
         <v>5</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW6" t="n">
         <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY6" t="n">
         <v>22</v>
@@ -1536,7 +1603,7 @@
         <v>12</v>
       </c>
       <c r="BA6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB6" t="n">
         <v>28</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1716,13 @@
         <v>-4.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
         <v>27</v>
       </c>
       <c r="AF7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG7" t="n">
         <v>27</v>
@@ -1664,7 +1731,7 @@
         <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ7" t="n">
         <v>3</v>
@@ -1679,7 +1746,7 @@
         <v>11</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO7" t="n">
         <v>14</v>
@@ -1688,10 +1755,10 @@
         <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS7" t="n">
         <v>30</v>
@@ -1700,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="AU7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV7" t="n">
         <v>7</v>
@@ -1709,7 +1776,7 @@
         <v>12</v>
       </c>
       <c r="AX7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY7" t="n">
         <v>29</v>
@@ -1721,7 +1788,7 @@
         <v>11</v>
       </c>
       <c r="BB7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BC7" t="n">
         <v>26</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -1753,28 +1820,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F8" t="n">
         <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.463</v>
+        <v>0.453</v>
       </c>
       <c r="H8" t="n">
         <v>48.9</v>
       </c>
       <c r="I8" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J8" t="n">
         <v>84.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L8" t="n">
         <v>7.3</v>
@@ -1789,22 +1856,22 @@
         <v>17.5</v>
       </c>
       <c r="P8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="R8" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S8" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="T8" t="n">
         <v>42.5</v>
       </c>
       <c r="U8" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V8" t="n">
         <v>14.1</v>
@@ -1813,7 +1880,7 @@
         <v>7.9</v>
       </c>
       <c r="X8" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="Y8" t="n">
         <v>4.4</v>
@@ -1825,22 +1892,22 @@
         <v>19.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>101.6</v>
+        <v>101.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF8" t="n">
         <v>17</v>
       </c>
       <c r="AG8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH8" t="n">
         <v>2</v>
@@ -1861,7 +1928,7 @@
         <v>12</v>
       </c>
       <c r="AN8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO8" t="n">
         <v>10</v>
@@ -1876,13 +1943,13 @@
         <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AT8" t="n">
         <v>14</v>
       </c>
       <c r="AU8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV8" t="n">
         <v>6</v>
@@ -1891,7 +1958,7 @@
         <v>16</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY8" t="n">
         <v>6</v>
@@ -1900,7 +1967,7 @@
         <v>24</v>
       </c>
       <c r="BA8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB8" t="n">
         <v>7</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E9" t="n">
         <v>34</v>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G9" t="n">
-        <v>0.607</v>
+        <v>0.618</v>
       </c>
       <c r="H9" t="n">
         <v>48.6</v>
@@ -1953,46 +2020,46 @@
         <v>40.2</v>
       </c>
       <c r="J9" t="n">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
       <c r="K9" t="n">
         <v>0.471</v>
       </c>
       <c r="L9" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M9" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.341</v>
+        <v>0.344</v>
       </c>
       <c r="O9" t="n">
-        <v>18.2</v>
+        <v>17.9</v>
       </c>
       <c r="P9" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="S9" t="n">
         <v>31.8</v>
       </c>
       <c r="T9" t="n">
-        <v>45.3</v>
+        <v>45.5</v>
       </c>
       <c r="U9" t="n">
         <v>23.9</v>
       </c>
       <c r="V9" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X9" t="n">
         <v>6.5</v>
@@ -2001,16 +2068,16 @@
         <v>6.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AB9" t="n">
-        <v>105.1</v>
+        <v>104.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD9" t="n">
         <v>5</v>
@@ -2019,10 +2086,10 @@
         <v>6</v>
       </c>
       <c r="AF9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH9" t="n">
         <v>6</v>
@@ -2037,13 +2104,13 @@
         <v>5</v>
       </c>
       <c r="AL9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM9" t="n">
         <v>17</v>
       </c>
       <c r="AN9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO9" t="n">
         <v>7</v>
@@ -2067,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW9" t="n">
         <v>3</v>
@@ -2088,7 +2155,7 @@
         <v>3</v>
       </c>
       <c r="BC9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -2117,58 +2184,58 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" t="n">
         <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
-        <v>0.386</v>
+        <v>0.393</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.3</v>
+        <v>36.5</v>
       </c>
       <c r="J10" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.445</v>
+        <v>0.447</v>
       </c>
       <c r="L10" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M10" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.365</v>
+        <v>0.369</v>
       </c>
       <c r="O10" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="P10" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.697</v>
       </c>
       <c r="R10" t="n">
         <v>12.6</v>
       </c>
       <c r="S10" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T10" t="n">
         <v>43.5</v>
       </c>
       <c r="U10" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V10" t="n">
         <v>15</v>
@@ -2183,22 +2250,22 @@
         <v>5.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AA10" t="n">
         <v>20.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>95.09999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.3</v>
+        <v>-1.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF10" t="n">
         <v>23</v>
@@ -2207,10 +2274,10 @@
         <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AJ10" t="n">
         <v>18</v>
@@ -2225,7 +2292,7 @@
         <v>25</v>
       </c>
       <c r="AN10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AO10" t="n">
         <v>22</v>
@@ -2234,13 +2301,13 @@
         <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
         <v>7</v>
@@ -2249,7 +2316,7 @@
         <v>24</v>
       </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
         <v>27</v>
@@ -2258,19 +2325,19 @@
         <v>8</v>
       </c>
       <c r="AY10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA10" t="n">
         <v>10</v>
       </c>
       <c r="BB10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -2299,43 +2366,43 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" t="n">
         <v>23</v>
       </c>
       <c r="G11" t="n">
-        <v>0.582</v>
+        <v>0.574</v>
       </c>
       <c r="H11" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I11" t="n">
         <v>38.1</v>
       </c>
       <c r="J11" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L11" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M11" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0.39</v>
+        <v>0.393</v>
       </c>
       <c r="O11" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P11" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="Q11" t="n">
         <v>0.797</v>
@@ -2344,16 +2411,16 @@
         <v>11</v>
       </c>
       <c r="S11" t="n">
-        <v>33.8</v>
+        <v>33.6</v>
       </c>
       <c r="T11" t="n">
-        <v>44.8</v>
+        <v>44.6</v>
       </c>
       <c r="U11" t="n">
         <v>22.9</v>
       </c>
       <c r="V11" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W11" t="n">
         <v>6.7</v>
@@ -2371,31 +2438,31 @@
         <v>19.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>101.2</v>
+        <v>101.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG11" t="n">
         <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
         <v>7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK11" t="n">
         <v>10</v>
@@ -2407,7 +2474,7 @@
         <v>13</v>
       </c>
       <c r="AN11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO11" t="n">
         <v>13</v>
@@ -2425,13 +2492,13 @@
         <v>1</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW11" t="n">
         <v>28</v>
@@ -2446,13 +2513,13 @@
         <v>28</v>
       </c>
       <c r="BA11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB11" t="n">
         <v>8</v>
       </c>
       <c r="BC11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" t="n">
         <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>0.544</v>
+        <v>0.536</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
@@ -2499,52 +2566,52 @@
         <v>38.5</v>
       </c>
       <c r="J12" t="n">
-        <v>83.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K12" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="L12" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="M12" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.367</v>
+        <v>0.364</v>
       </c>
       <c r="O12" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="P12" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R12" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S12" t="n">
         <v>32.2</v>
       </c>
       <c r="T12" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U12" t="n">
         <v>23.3</v>
       </c>
       <c r="V12" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="W12" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X12" t="n">
         <v>4.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Z12" t="n">
         <v>20.2</v>
@@ -2556,13 +2623,13 @@
         <v>106.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF12" t="n">
         <v>14</v>
@@ -2577,7 +2644,7 @@
         <v>4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK12" t="n">
         <v>6</v>
@@ -2589,10 +2656,10 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP12" t="n">
         <v>6</v>
@@ -2601,16 +2668,16 @@
         <v>16</v>
       </c>
       <c r="AR12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT12" t="n">
         <v>10</v>
       </c>
       <c r="AU12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
@@ -2628,10 +2695,10 @@
         <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -2663,64 +2730,64 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F13" t="n">
         <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>0.618</v>
+        <v>0.611</v>
       </c>
       <c r="H13" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I13" t="n">
-        <v>35.1</v>
+        <v>34.9</v>
       </c>
       <c r="J13" t="n">
-        <v>81</v>
+        <v>81.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0.433</v>
+        <v>0.431</v>
       </c>
       <c r="L13" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M13" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0.355</v>
+        <v>0.35</v>
       </c>
       <c r="O13" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P13" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.741</v>
+        <v>0.743</v>
       </c>
       <c r="R13" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S13" t="n">
-        <v>33.1</v>
+        <v>32.9</v>
       </c>
       <c r="T13" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="U13" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="V13" t="n">
         <v>15</v>
       </c>
       <c r="W13" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X13" t="n">
         <v>6.7</v>
@@ -2732,25 +2799,25 @@
         <v>19.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>93.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF13" t="n">
         <v>7</v>
       </c>
       <c r="AG13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH13" t="n">
         <v>10</v>
@@ -2759,22 +2826,22 @@
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM13" t="n">
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AO13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP13" t="n">
         <v>13</v>
@@ -2783,19 +2850,19 @@
         <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
       </c>
       <c r="AU13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW13" t="n">
         <v>26</v>
@@ -2804,19 +2871,19 @@
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA13" t="n">
         <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2993,7 @@
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>4</v>
@@ -2941,7 +3008,7 @@
         <v>8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK14" t="n">
         <v>4</v>
@@ -2956,7 +3023,7 @@
         <v>12</v>
       </c>
       <c r="AO14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP14" t="n">
         <v>9</v>
@@ -2974,10 +3041,10 @@
         <v>17</v>
       </c>
       <c r="AU14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -3027,55 +3094,55 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" t="n">
         <v>29</v>
       </c>
       <c r="G15" t="n">
-        <v>0.482</v>
+        <v>0.473</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K15" t="n">
         <v>0.458</v>
       </c>
       <c r="L15" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="M15" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="N15" t="n">
         <v>0.351</v>
       </c>
       <c r="O15" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P15" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.695</v>
+        <v>0.694</v>
       </c>
       <c r="R15" t="n">
         <v>11.7</v>
       </c>
       <c r="S15" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="T15" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="U15" t="n">
         <v>22.2</v>
@@ -3093,13 +3160,13 @@
         <v>5</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>102</v>
+        <v>101.8</v>
       </c>
       <c r="AC15" t="n">
         <v>1</v>
@@ -3126,7 +3193,7 @@
         <v>19</v>
       </c>
       <c r="AK15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL15" t="n">
         <v>5</v>
@@ -3135,43 +3202,43 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP15" t="n">
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR15" t="n">
         <v>12</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AT15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AV15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW15" t="n">
         <v>22</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F16" t="n">
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>0.667</v>
+        <v>0.66</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
@@ -3227,43 +3294,43 @@
         <v>36.4</v>
       </c>
       <c r="J16" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L16" t="n">
         <v>4.7</v>
       </c>
       <c r="M16" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0.344</v>
+        <v>0.347</v>
       </c>
       <c r="O16" t="n">
         <v>16.3</v>
       </c>
       <c r="P16" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.781</v>
+        <v>0.786</v>
       </c>
       <c r="R16" t="n">
         <v>13.5</v>
       </c>
       <c r="S16" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T16" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="U16" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V16" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W16" t="n">
         <v>8.9</v>
@@ -3272,22 +3339,22 @@
         <v>5.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z16" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="AA16" t="n">
         <v>19.8</v>
       </c>
-      <c r="AA16" t="n">
-        <v>19.9</v>
-      </c>
       <c r="AB16" t="n">
-        <v>93.7</v>
+        <v>93.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>5</v>
@@ -3299,25 +3366,25 @@
         <v>5</v>
       </c>
       <c r="AH16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK16" t="n">
         <v>22</v>
       </c>
       <c r="AL16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM16" t="n">
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
         <v>21</v>
@@ -3326,7 +3393,7 @@
         <v>24</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR16" t="n">
         <v>2</v>
@@ -3335,7 +3402,7 @@
         <v>27</v>
       </c>
       <c r="AT16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU16" t="n">
         <v>23</v>
@@ -3350,16 +3417,16 @@
         <v>15</v>
       </c>
       <c r="AY16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC16" t="n">
         <v>6</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>6.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
@@ -3508,7 +3575,7 @@
         <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR17" t="n">
         <v>28</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV17" t="n">
         <v>4</v>
@@ -3535,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
         <v>12</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3718,10 @@
         <v>-1.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF18" t="n">
         <v>16</v>
@@ -3675,13 +3742,13 @@
         <v>26</v>
       </c>
       <c r="AL18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AN18" t="n">
         <v>21</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>22</v>
       </c>
       <c r="AO18" t="n">
         <v>24</v>
@@ -3693,22 +3760,22 @@
         <v>24</v>
       </c>
       <c r="AR18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT18" t="n">
         <v>6</v>
       </c>
       <c r="AU18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV18" t="n">
         <v>8</v>
       </c>
       <c r="AW18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX18" t="n">
         <v>1</v>
@@ -3720,13 +3787,13 @@
         <v>10</v>
       </c>
       <c r="BA18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB18" t="n">
         <v>12</v>
       </c>
       <c r="BC18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -3755,61 +3822,61 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E19" t="n">
         <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G19" t="n">
-        <v>0.385</v>
+        <v>0.392</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J19" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K19" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L19" t="n">
         <v>5.5</v>
       </c>
       <c r="M19" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.303</v>
+        <v>0.302</v>
       </c>
       <c r="O19" t="n">
         <v>18.9</v>
       </c>
       <c r="P19" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.734</v>
+        <v>0.733</v>
       </c>
       <c r="R19" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S19" t="n">
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
       <c r="T19" t="n">
-        <v>43.2</v>
+        <v>43.5</v>
       </c>
       <c r="U19" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V19" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W19" t="n">
         <v>8</v>
@@ -3821,19 +3888,19 @@
         <v>6</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AA19" t="n">
         <v>22.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.2</v>
+        <v>-1.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE19" t="n">
         <v>23</v>
@@ -3878,16 +3945,16 @@
         <v>5</v>
       </c>
       <c r="AS19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU19" t="n">
         <v>19</v>
       </c>
       <c r="AV19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
         <v>14</v>
@@ -3896,19 +3963,19 @@
         <v>18</v>
       </c>
       <c r="AY19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" t="n">
         <v>19</v>
       </c>
       <c r="F20" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G20" t="n">
-        <v>0.339</v>
+        <v>0.345</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3955,28 +4022,28 @@
         <v>36.2</v>
       </c>
       <c r="J20" t="n">
-        <v>80.2</v>
+        <v>80</v>
       </c>
       <c r="K20" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L20" t="n">
         <v>6.8</v>
       </c>
       <c r="M20" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.373</v>
+        <v>0.375</v>
       </c>
       <c r="O20" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="P20" t="n">
         <v>19.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.767</v>
+        <v>0.764</v>
       </c>
       <c r="R20" t="n">
         <v>11.2</v>
@@ -3985,10 +4052,10 @@
         <v>30.1</v>
       </c>
       <c r="T20" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U20" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V20" t="n">
         <v>14.6</v>
@@ -4000,7 +4067,7 @@
         <v>5.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="Z20" t="n">
         <v>20.5</v>
@@ -4009,7 +4076,7 @@
         <v>18.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>94.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC20" t="n">
         <v>-3.1</v>
@@ -4030,16 +4097,16 @@
         <v>19</v>
       </c>
       <c r="AI20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ20" t="n">
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM20" t="n">
         <v>21</v>
@@ -4051,13 +4118,13 @@
         <v>25</v>
       </c>
       <c r="AP20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ20" t="n">
         <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AS20" t="n">
         <v>21</v>
@@ -4069,16 +4136,16 @@
         <v>21</v>
       </c>
       <c r="AV20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW20" t="n">
         <v>29</v>
       </c>
       <c r="AX20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY20" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ20" t="n">
         <v>21</v>
@@ -4087,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="BB20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC20" t="n">
         <v>23</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E21" t="n">
         <v>32</v>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G21" t="n">
-        <v>0.615</v>
+        <v>0.627</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
@@ -4137,7 +4204,7 @@
         <v>36.6</v>
       </c>
       <c r="J21" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K21" t="n">
         <v>0.443</v>
@@ -4146,13 +4213,13 @@
         <v>10.9</v>
       </c>
       <c r="M21" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="N21" t="n">
         <v>0.377</v>
       </c>
       <c r="O21" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="P21" t="n">
         <v>21.3</v>
@@ -4164,40 +4231,40 @@
         <v>11.2</v>
       </c>
       <c r="S21" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T21" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U21" t="n">
         <v>19.6</v>
       </c>
       <c r="V21" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="W21" t="n">
         <v>8.1</v>
       </c>
       <c r="X21" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="AA21" t="n">
         <v>19.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>100.1</v>
+        <v>100.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE21" t="n">
         <v>9</v>
@@ -4206,7 +4273,7 @@
         <v>6</v>
       </c>
       <c r="AG21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH21" t="n">
         <v>27</v>
@@ -4215,7 +4282,7 @@
         <v>17</v>
       </c>
       <c r="AJ21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK21" t="n">
         <v>17</v>
@@ -4233,16 +4300,16 @@
         <v>23</v>
       </c>
       <c r="AP21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR21" t="n">
         <v>17</v>
       </c>
       <c r="AS21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT21" t="n">
         <v>23</v>
@@ -4257,7 +4324,7 @@
         <v>13</v>
       </c>
       <c r="AX21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY21" t="n">
         <v>2</v>
@@ -4266,13 +4333,13 @@
         <v>9</v>
       </c>
       <c r="BA21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB21" t="n">
         <v>10</v>
       </c>
       <c r="BC21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -4301,46 +4368,46 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E22" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F22" t="n">
         <v>15</v>
       </c>
       <c r="G22" t="n">
-        <v>0.727</v>
+        <v>0.722</v>
       </c>
       <c r="H22" t="n">
         <v>48.5</v>
       </c>
       <c r="I22" t="n">
-        <v>38.3</v>
+        <v>38.1</v>
       </c>
       <c r="J22" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="K22" t="n">
-        <v>0.483</v>
+        <v>0.482</v>
       </c>
       <c r="L22" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M22" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.392</v>
+        <v>0.389</v>
       </c>
       <c r="O22" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="P22" t="n">
         <v>26.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.832</v>
+        <v>0.83</v>
       </c>
       <c r="R22" t="n">
         <v>10.2</v>
@@ -4352,10 +4419,10 @@
         <v>42.8</v>
       </c>
       <c r="U22" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="V22" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W22" t="n">
         <v>8.4</v>
@@ -4364,22 +4431,22 @@
         <v>7.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA22" t="n">
         <v>21</v>
       </c>
       <c r="AB22" t="n">
-        <v>106.7</v>
+        <v>106.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI22" t="n">
         <v>6</v>
@@ -4409,7 +4476,7 @@
         <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4427,16 +4494,16 @@
         <v>6</v>
       </c>
       <c r="AT22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV22" t="n">
         <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4451,10 +4518,10 @@
         <v>8</v>
       </c>
       <c r="BB22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -4483,88 +4550,88 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E23" t="n">
         <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
-        <v>0.273</v>
+        <v>0.278</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="J23" t="n">
         <v>83.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L23" t="n">
         <v>6.5</v>
       </c>
       <c r="M23" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="N23" t="n">
         <v>0.337</v>
       </c>
       <c r="O23" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="P23" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="Q23" t="n">
         <v>0.769</v>
       </c>
       <c r="R23" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S23" t="n">
         <v>32.2</v>
       </c>
       <c r="T23" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U23" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="V23" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W23" t="n">
         <v>6</v>
       </c>
       <c r="X23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y23" t="n">
         <v>5</v>
       </c>
       <c r="Z23" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA23" t="n">
         <v>16.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>93.8</v>
+        <v>94</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.7</v>
+        <v>-5.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF23" t="n">
         <v>29</v>
@@ -4579,13 +4646,13 @@
         <v>10</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK23" t="n">
         <v>14</v>
       </c>
       <c r="AL23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM23" t="n">
         <v>16</v>
@@ -4606,25 +4673,25 @@
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
       </c>
       <c r="AX23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ23" t="n">
         <v>7</v>
@@ -4633,7 +4700,7 @@
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC23" t="n">
         <v>28</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -4743,13 +4810,13 @@
         <v>-3.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG24" t="n">
         <v>20</v>
@@ -4764,7 +4831,7 @@
         <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL24" t="n">
         <v>24</v>
@@ -4773,7 +4840,7 @@
         <v>23</v>
       </c>
       <c r="AN24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4785,7 +4852,7 @@
         <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS24" t="n">
         <v>15</v>
@@ -4794,7 +4861,7 @@
         <v>18</v>
       </c>
       <c r="AU24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -4847,22 +4914,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E25" t="n">
         <v>18</v>
       </c>
       <c r="F25" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G25" t="n">
-        <v>0.321</v>
+        <v>0.327</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
       </c>
       <c r="I25" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J25" t="n">
         <v>83.90000000000001</v>
@@ -4871,34 +4938,34 @@
         <v>0.444</v>
       </c>
       <c r="L25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M25" t="n">
         <v>17.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.325</v>
+        <v>0.327</v>
       </c>
       <c r="O25" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="P25" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.752</v>
+        <v>0.755</v>
       </c>
       <c r="R25" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S25" t="n">
         <v>29.8</v>
       </c>
       <c r="T25" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U25" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="V25" t="n">
         <v>14.7</v>
@@ -4910,19 +4977,19 @@
         <v>5.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>94.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>-5.6</v>
+        <v>-5.2</v>
       </c>
       <c r="AD25" t="n">
         <v>5</v>
@@ -4931,7 +4998,7 @@
         <v>26</v>
       </c>
       <c r="AF25" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG25" t="n">
         <v>26</v>
@@ -4940,7 +5007,7 @@
         <v>24</v>
       </c>
       <c r="AI25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AJ25" t="n">
         <v>5</v>
@@ -4958,13 +5025,13 @@
         <v>29</v>
       </c>
       <c r="AO25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP25" t="n">
         <v>27</v>
       </c>
-      <c r="AP25" t="n">
-        <v>26</v>
-      </c>
       <c r="AQ25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR25" t="n">
         <v>15</v>
@@ -4976,7 +5043,7 @@
         <v>22</v>
       </c>
       <c r="AU25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AV25" t="n">
         <v>14</v>
@@ -4985,13 +5052,13 @@
         <v>17</v>
       </c>
       <c r="AX25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
         <v>17</v>
       </c>
       <c r="AZ25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA25" t="n">
         <v>28</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -5029,28 +5096,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G26" t="n">
-        <v>0.455</v>
+        <v>0.463</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="J26" t="n">
-        <v>82</v>
+        <v>81.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L26" t="n">
         <v>8</v>
@@ -5059,28 +5126,28 @@
         <v>23.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.338</v>
+        <v>0.337</v>
       </c>
       <c r="O26" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="P26" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.778</v>
+        <v>0.78</v>
       </c>
       <c r="R26" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S26" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T26" t="n">
         <v>41.4</v>
       </c>
       <c r="U26" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V26" t="n">
         <v>15</v>
@@ -5095,40 +5162,40 @@
         <v>4.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>96.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="AC26" t="n">
         <v>-3</v>
       </c>
       <c r="AD26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
       </c>
       <c r="AF26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH26" t="n">
         <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AJ26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="n">
         <v>7</v>
@@ -5140,16 +5207,16 @@
         <v>27</v>
       </c>
       <c r="AO26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AS26" t="n">
         <v>18</v>
@@ -5161,13 +5228,13 @@
         <v>22</v>
       </c>
       <c r="AV26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW26" t="n">
         <v>25</v>
       </c>
       <c r="AX26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5176,7 +5243,7 @@
         <v>6</v>
       </c>
       <c r="BA26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB26" t="n">
         <v>17</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E27" t="n">
         <v>19</v>
       </c>
       <c r="F27" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G27" t="n">
-        <v>0.339</v>
+        <v>0.345</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5229,19 +5296,19 @@
         <v>36.4</v>
       </c>
       <c r="J27" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K27" t="n">
         <v>0.438</v>
       </c>
       <c r="L27" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M27" t="n">
         <v>18.6</v>
       </c>
       <c r="N27" t="n">
-        <v>0.355</v>
+        <v>0.351</v>
       </c>
       <c r="O27" t="n">
         <v>17.6</v>
@@ -5250,43 +5317,43 @@
         <v>23.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="R27" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S27" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="T27" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U27" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V27" t="n">
         <v>14.9</v>
       </c>
       <c r="W27" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X27" t="n">
         <v>4.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Z27" t="n">
         <v>21.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>97.09999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>-7.1</v>
+        <v>-6.9</v>
       </c>
       <c r="AD27" t="n">
         <v>5</v>
@@ -5304,22 +5371,22 @@
         <v>19</v>
       </c>
       <c r="AI27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN27" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AO27" t="n">
         <v>9</v>
@@ -5328,7 +5395,7 @@
         <v>11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR27" t="n">
         <v>11</v>
@@ -5343,10 +5410,10 @@
         <v>28</v>
       </c>
       <c r="AV27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX27" t="n">
         <v>24</v>
@@ -5358,7 +5425,7 @@
         <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB27" t="n">
         <v>15</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -5393,61 +5460,61 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E28" t="n">
         <v>44</v>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G28" t="n">
-        <v>0.772</v>
+        <v>0.786</v>
       </c>
       <c r="H28" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I28" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="J28" t="n">
-        <v>81.2</v>
+        <v>81</v>
       </c>
       <c r="K28" t="n">
-        <v>0.487</v>
+        <v>0.489</v>
       </c>
       <c r="L28" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="M28" t="n">
         <v>22.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0.381</v>
+        <v>0.384</v>
       </c>
       <c r="O28" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P28" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.79</v>
+        <v>0.792</v>
       </c>
       <c r="R28" t="n">
         <v>7.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.1</v>
+        <v>32.9</v>
       </c>
       <c r="T28" t="n">
-        <v>41</v>
+        <v>40.8</v>
       </c>
       <c r="U28" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="V28" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W28" t="n">
         <v>8.699999999999999</v>
@@ -5459,19 +5526,19 @@
         <v>4.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.4</v>
+        <v>104.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5483,13 +5550,13 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AI28" t="n">
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5504,10 +5571,10 @@
         <v>4</v>
       </c>
       <c r="AO28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ28" t="n">
         <v>4</v>
@@ -5516,10 +5583,10 @@
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -5546,7 +5613,7 @@
         <v>4</v>
       </c>
       <c r="BC28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F29" t="n">
         <v>33</v>
       </c>
       <c r="G29" t="n">
-        <v>0.411</v>
+        <v>0.4</v>
       </c>
       <c r="H29" t="n">
         <v>48.9</v>
@@ -5593,7 +5660,7 @@
         <v>36.3</v>
       </c>
       <c r="J29" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K29" t="n">
         <v>0.443</v>
@@ -5605,31 +5672,31 @@
         <v>21.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="O29" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P29" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R29" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S29" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="T29" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="U29" t="n">
         <v>22.1</v>
       </c>
       <c r="V29" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W29" t="n">
         <v>7.4</v>
@@ -5638,19 +5705,19 @@
         <v>4.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z29" t="n">
         <v>22.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="AB29" t="n">
         <v>97.40000000000001</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
       <c r="AD29" t="n">
         <v>5</v>
@@ -5668,10 +5735,10 @@
         <v>3</v>
       </c>
       <c r="AI29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK29" t="n">
         <v>18</v>
@@ -5692,7 +5759,7 @@
         <v>15</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AR29" t="n">
         <v>20</v>
@@ -5701,10 +5768,10 @@
         <v>28</v>
       </c>
       <c r="AT29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AV29" t="n">
         <v>3</v>
@@ -5722,7 +5789,7 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB29" t="n">
         <v>13</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -5835,34 +5902,34 @@
         <v>-0.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AF30" t="n">
         <v>13</v>
       </c>
       <c r="AG30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH30" t="n">
         <v>13</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>12</v>
       </c>
       <c r="AI30" t="n">
         <v>15</v>
       </c>
       <c r="AJ30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL30" t="n">
         <v>23</v>
       </c>
       <c r="AM30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AN30" t="n">
         <v>10</v>
@@ -5871,7 +5938,7 @@
         <v>6</v>
       </c>
       <c r="AP30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ30" t="n">
         <v>11</v>
@@ -5886,22 +5953,22 @@
         <v>16</v>
       </c>
       <c r="AU30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV30" t="n">
         <v>16</v>
       </c>
       <c r="AW30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX30" t="n">
         <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA30" t="n">
         <v>9</v>
@@ -5910,7 +5977,7 @@
         <v>11</v>
       </c>
       <c r="BC30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
@@ -5939,91 +6006,91 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
         <v>37</v>
       </c>
       <c r="G31" t="n">
-        <v>0.302</v>
+        <v>0.288</v>
       </c>
       <c r="H31" t="n">
         <v>48.7</v>
       </c>
       <c r="I31" t="n">
-        <v>35.3</v>
+        <v>35.1</v>
       </c>
       <c r="J31" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.428</v>
+        <v>0.427</v>
       </c>
       <c r="L31" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M31" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0.348</v>
+        <v>0.346</v>
       </c>
       <c r="O31" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="P31" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.734</v>
+        <v>0.735</v>
       </c>
       <c r="R31" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S31" t="n">
         <v>32.5</v>
       </c>
       <c r="T31" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U31" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V31" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W31" t="n">
         <v>7.5</v>
       </c>
       <c r="X31" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y31" t="n">
         <v>4.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>91.8</v>
+        <v>91.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.8</v>
+        <v>-4</v>
       </c>
       <c r="AD31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
       </c>
       <c r="AF31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG31" t="n">
         <v>28</v>
@@ -6041,16 +6108,16 @@
         <v>29</v>
       </c>
       <c r="AL31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AM31" t="n">
         <v>18</v>
       </c>
       <c r="AN31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP31" t="n">
         <v>25</v>
@@ -6065,7 +6132,7 @@
         <v>7</v>
       </c>
       <c r="AT31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU31" t="n">
         <v>20</v>
@@ -6077,7 +6144,7 @@
         <v>18</v>
       </c>
       <c r="AX31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY31" t="n">
         <v>13</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-22-2012-13</t>
+          <t>2013-02-22</t>
         </is>
       </c>
     </row>
